--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7245,6 +7245,539 @@
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122534080</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>580937</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6384897</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122537418</v>
+      </c>
+      <c r="B59" t="n">
+        <v>105317</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221144</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>581093</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6384901</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122537449</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57395</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>581078</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6384903</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122534099</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98211</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>580969</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6384921</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122537789</v>
+      </c>
+      <c r="B62" t="n">
+        <v>105317</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221144</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>581038</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6384962</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122534080</v>
+        <v>122537449</v>
       </c>
       <c r="B58" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,34 +7259,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7294,13 +7295,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580937</v>
+        <v>581078</v>
       </c>
       <c r="R58" t="n">
-        <v>6384897</v>
+        <v>6384903</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7338,19 +7339,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7360,7 +7360,7 @@
         <v>122537418</v>
       </c>
       <c r="B59" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7374,6 +7374,11 @@
       </c>
       <c r="E59" t="n">
         <v>221144</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7463,10 +7468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537449</v>
+        <v>122534080</v>
       </c>
       <c r="B60" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7475,30 +7480,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7506,13 +7520,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581078</v>
+        <v>580937</v>
       </c>
       <c r="R60" t="n">
-        <v>6384903</v>
+        <v>6384897</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7550,18 +7564,19 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7571,7 +7586,7 @@
         <v>122534099</v>
       </c>
       <c r="B61" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7585,6 +7600,11 @@
       </c>
       <c r="E61" t="n">
         <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7681,7 +7701,7 @@
         <v>122537789</v>
       </c>
       <c r="B62" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7695,6 +7715,11 @@
       </c>
       <c r="E62" t="n">
         <v>221144</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122537449</v>
+        <v>122537789</v>
       </c>
       <c r="B58" t="n">
-        <v>57399</v>
+        <v>105343</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,35 +7259,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7295,10 +7291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581078</v>
+        <v>581038</v>
       </c>
       <c r="R58" t="n">
-        <v>6384903</v>
+        <v>6384962</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7339,6 +7335,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7357,10 +7354,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122537418</v>
+        <v>122534099</v>
       </c>
       <c r="B59" t="n">
-        <v>105330</v>
+        <v>98237</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7369,28 +7366,32 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7405,13 +7406,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581093</v>
+        <v>580969</v>
       </c>
       <c r="R59" t="n">
-        <v>6384901</v>
+        <v>6384921</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7456,22 +7457,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122534080</v>
+        <v>122537449</v>
       </c>
       <c r="B60" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7480,39 +7481,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7520,13 +7517,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580937</v>
+        <v>581078</v>
       </c>
       <c r="R60" t="n">
-        <v>6384897</v>
+        <v>6384903</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7564,29 +7561,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122534099</v>
+        <v>122534080</v>
       </c>
       <c r="B61" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7618,7 +7614,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7635,10 +7631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580969</v>
+        <v>580937</v>
       </c>
       <c r="R61" t="n">
-        <v>6384921</v>
+        <v>6384897</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7698,10 +7694,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122537789</v>
+        <v>122537418</v>
       </c>
       <c r="B62" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7732,7 +7728,11 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7742,10 +7742,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581038</v>
+        <v>581093</v>
       </c>
       <c r="R62" t="n">
-        <v>6384962</v>
+        <v>6384901</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7354,10 +7354,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122534099</v>
+        <v>122537449</v>
       </c>
       <c r="B59" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7366,39 +7366,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7406,13 +7402,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580969</v>
+        <v>581078</v>
       </c>
       <c r="R59" t="n">
-        <v>6384921</v>
+        <v>6384903</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7450,29 +7446,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537449</v>
+        <v>122537418</v>
       </c>
       <c r="B60" t="n">
-        <v>57399</v>
+        <v>105343</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7481,35 +7476,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7517,10 +7512,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581078</v>
+        <v>581093</v>
       </c>
       <c r="R60" t="n">
-        <v>6384903</v>
+        <v>6384901</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7561,6 +7556,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7694,10 +7690,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122537418</v>
+        <v>122534099</v>
       </c>
       <c r="B62" t="n">
-        <v>105343</v>
+        <v>98237</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7706,28 +7702,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7742,13 +7742,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581093</v>
+        <v>580969</v>
       </c>
       <c r="R62" t="n">
-        <v>6384901</v>
+        <v>6384921</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7793,12 +7793,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122537789</v>
+        <v>122534099</v>
       </c>
       <c r="B58" t="n">
-        <v>105343</v>
+        <v>98240</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,29 +7259,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7291,13 +7299,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581038</v>
+        <v>580969</v>
       </c>
       <c r="R58" t="n">
-        <v>6384962</v>
+        <v>6384921</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,12 +7350,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7464,10 +7472,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537418</v>
+        <v>122537789</v>
       </c>
       <c r="B60" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7498,11 +7506,7 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7512,10 +7516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581093</v>
+        <v>581038</v>
       </c>
       <c r="R60" t="n">
-        <v>6384901</v>
+        <v>6384962</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7575,10 +7579,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122534080</v>
+        <v>122537418</v>
       </c>
       <c r="B61" t="n">
-        <v>98237</v>
+        <v>105346</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7587,32 +7591,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580937</v>
+        <v>581093</v>
       </c>
       <c r="R61" t="n">
-        <v>6384897</v>
+        <v>6384901</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7678,22 +7678,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122534099</v>
+        <v>122534080</v>
       </c>
       <c r="B62" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7742,10 +7742,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580969</v>
+        <v>580937</v>
       </c>
       <c r="R62" t="n">
-        <v>6384921</v>
+        <v>6384897</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122534099</v>
+        <v>122537789</v>
       </c>
       <c r="B58" t="n">
-        <v>98240</v>
+        <v>105346</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,37 +7259,29 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7299,13 +7291,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580969</v>
+        <v>581038</v>
       </c>
       <c r="R58" t="n">
-        <v>6384921</v>
+        <v>6384962</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7350,12 +7342,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7472,10 +7464,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537789</v>
+        <v>122534080</v>
       </c>
       <c r="B60" t="n">
-        <v>105346</v>
+        <v>98240</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7484,29 +7476,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7516,13 +7516,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581038</v>
+        <v>580937</v>
       </c>
       <c r="R60" t="n">
-        <v>6384962</v>
+        <v>6384897</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7567,12 +7567,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122534080</v>
+        <v>122534099</v>
       </c>
       <c r="B62" t="n">
         <v>98240</v>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7742,10 +7742,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580937</v>
+        <v>580969</v>
       </c>
       <c r="R62" t="n">
-        <v>6384897</v>
+        <v>6384921</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122537789</v>
+        <v>122537449</v>
       </c>
       <c r="B58" t="n">
-        <v>105346</v>
+        <v>57400</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,31 +7259,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7291,10 +7295,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581038</v>
+        <v>581078</v>
       </c>
       <c r="R58" t="n">
-        <v>6384962</v>
+        <v>6384903</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7335,7 +7339,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7354,10 +7357,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122537449</v>
+        <v>122534080</v>
       </c>
       <c r="B59" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7366,35 +7369,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7402,13 +7409,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581078</v>
+        <v>580937</v>
       </c>
       <c r="R59" t="n">
-        <v>6384903</v>
+        <v>6384897</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7446,28 +7453,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122534080</v>
+        <v>122534099</v>
       </c>
       <c r="B60" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7499,7 +7507,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7516,10 +7524,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580937</v>
+        <v>580969</v>
       </c>
       <c r="R60" t="n">
-        <v>6384897</v>
+        <v>6384921</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7579,10 +7587,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122537418</v>
+        <v>122537789</v>
       </c>
       <c r="B61" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7613,11 +7621,7 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7627,10 +7631,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581093</v>
+        <v>581038</v>
       </c>
       <c r="R61" t="n">
-        <v>6384901</v>
+        <v>6384962</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7690,10 +7694,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122534099</v>
+        <v>122537418</v>
       </c>
       <c r="B62" t="n">
-        <v>98240</v>
+        <v>105347</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7702,32 +7706,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7742,13 +7742,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580969</v>
+        <v>581093</v>
       </c>
       <c r="R62" t="n">
-        <v>6384921</v>
+        <v>6384901</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7793,12 +7793,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122537449</v>
+        <v>122534080</v>
       </c>
       <c r="B58" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,35 +7259,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7295,13 +7299,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581078</v>
+        <v>580937</v>
       </c>
       <c r="R58" t="n">
-        <v>6384903</v>
+        <v>6384897</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7339,28 +7343,29 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122534080</v>
+        <v>122537789</v>
       </c>
       <c r="B59" t="n">
-        <v>98241</v>
+        <v>105350</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7369,37 +7374,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -7409,13 +7406,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580937</v>
+        <v>581038</v>
       </c>
       <c r="R59" t="n">
-        <v>6384897</v>
+        <v>6384962</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7460,22 +7457,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122534099</v>
+        <v>122537449</v>
       </c>
       <c r="B60" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7484,39 +7481,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7524,13 +7517,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580969</v>
+        <v>581078</v>
       </c>
       <c r="R60" t="n">
-        <v>6384921</v>
+        <v>6384903</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7568,29 +7561,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122537789</v>
+        <v>122534099</v>
       </c>
       <c r="B61" t="n">
-        <v>105347</v>
+        <v>98244</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7599,29 +7591,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7631,13 +7631,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581038</v>
+        <v>580969</v>
       </c>
       <c r="R61" t="n">
-        <v>6384962</v>
+        <v>6384921</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7682,12 +7682,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7697,7 +7697,7 @@
         <v>122537418</v>
       </c>
       <c r="B62" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122534080</v>
+        <v>122537418</v>
       </c>
       <c r="B58" t="n">
-        <v>98244</v>
+        <v>105350</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,32 +7259,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7299,13 +7295,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580937</v>
+        <v>581093</v>
       </c>
       <c r="R58" t="n">
-        <v>6384897</v>
+        <v>6384901</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7350,22 +7346,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122537789</v>
+        <v>122534080</v>
       </c>
       <c r="B59" t="n">
-        <v>105350</v>
+        <v>98244</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7374,29 +7370,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -7406,13 +7410,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581038</v>
+        <v>580937</v>
       </c>
       <c r="R59" t="n">
-        <v>6384962</v>
+        <v>6384897</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7457,22 +7461,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537449</v>
+        <v>122534099</v>
       </c>
       <c r="B60" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7481,35 +7485,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7517,13 +7525,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581078</v>
+        <v>580969</v>
       </c>
       <c r="R60" t="n">
-        <v>6384903</v>
+        <v>6384921</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7561,28 +7569,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122534099</v>
+        <v>122537789</v>
       </c>
       <c r="B61" t="n">
-        <v>98244</v>
+        <v>105350</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7591,37 +7600,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7631,13 +7632,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580969</v>
+        <v>581038</v>
       </c>
       <c r="R61" t="n">
-        <v>6384921</v>
+        <v>6384962</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7682,22 +7683,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122537418</v>
+        <v>122537449</v>
       </c>
       <c r="B62" t="n">
-        <v>105350</v>
+        <v>57400</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7706,35 +7707,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7742,10 +7743,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581093</v>
+        <v>581078</v>
       </c>
       <c r="R62" t="n">
-        <v>6384901</v>
+        <v>6384903</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7786,7 +7787,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7250,7 +7250,7 @@
         <v>122537418</v>
       </c>
       <c r="B58" t="n">
-        <v>105350</v>
+        <v>105453</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
         <v>122534080</v>
       </c>
       <c r="B59" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122534099</v>
+        <v>122537789</v>
       </c>
       <c r="B60" t="n">
-        <v>98244</v>
+        <v>105453</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7485,37 +7485,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7525,13 +7517,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580969</v>
+        <v>581038</v>
       </c>
       <c r="R60" t="n">
-        <v>6384921</v>
+        <v>6384962</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7576,22 +7568,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122537789</v>
+        <v>122534099</v>
       </c>
       <c r="B61" t="n">
-        <v>105350</v>
+        <v>98347</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7600,29 +7592,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7632,13 +7632,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581038</v>
+        <v>580969</v>
       </c>
       <c r="R61" t="n">
-        <v>6384962</v>
+        <v>6384921</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7683,12 +7683,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7698,7 +7698,7 @@
         <v>122537449</v>
       </c>
       <c r="B62" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122537418</v>
+        <v>122537789</v>
       </c>
       <c r="B58" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7281,11 +7281,7 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7295,10 +7291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581093</v>
+        <v>581038</v>
       </c>
       <c r="R58" t="n">
-        <v>6384901</v>
+        <v>6384962</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7351,17 +7347,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122534080</v>
+        <v>122537449</v>
       </c>
       <c r="B59" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7370,39 +7366,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7410,13 +7402,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580937</v>
+        <v>581078</v>
       </c>
       <c r="R59" t="n">
-        <v>6384897</v>
+        <v>6384903</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7454,29 +7446,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537789</v>
+        <v>122534080</v>
       </c>
       <c r="B60" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7485,29 +7476,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7517,13 +7516,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581038</v>
+        <v>580937</v>
       </c>
       <c r="R60" t="n">
-        <v>6384962</v>
+        <v>6384897</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7568,22 +7567,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122534099</v>
+        <v>122537418</v>
       </c>
       <c r="B61" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7592,32 +7591,28 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7632,13 +7627,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580969</v>
+        <v>581093</v>
       </c>
       <c r="R61" t="n">
-        <v>6384921</v>
+        <v>6384901</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7683,22 +7678,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122537449</v>
+        <v>122534099</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7707,35 +7702,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7743,13 +7742,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581078</v>
+        <v>580969</v>
       </c>
       <c r="R62" t="n">
-        <v>6384903</v>
+        <v>6384921</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7787,13 +7786,14 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122537789</v>
+        <v>122534099</v>
       </c>
       <c r="B58" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,29 +7259,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7291,13 +7299,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581038</v>
+        <v>580969</v>
       </c>
       <c r="R58" t="n">
-        <v>6384962</v>
+        <v>6384921</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7342,22 +7350,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122537449</v>
+        <v>122537789</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>105461</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7366,35 +7374,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7402,10 +7406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581078</v>
+        <v>581038</v>
       </c>
       <c r="R59" t="n">
-        <v>6384903</v>
+        <v>6384962</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7446,6 +7450,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7464,10 +7469,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122534080</v>
+        <v>122537449</v>
       </c>
       <c r="B60" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7476,39 +7481,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7516,13 +7517,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580937</v>
+        <v>581078</v>
       </c>
       <c r="R60" t="n">
-        <v>6384897</v>
+        <v>6384903</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7560,29 +7561,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122537418</v>
+        <v>122534080</v>
       </c>
       <c r="B61" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7591,28 +7591,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7627,13 +7631,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581093</v>
+        <v>580937</v>
       </c>
       <c r="R61" t="n">
-        <v>6384901</v>
+        <v>6384897</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7678,22 +7682,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122534099</v>
+        <v>122537418</v>
       </c>
       <c r="B62" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7702,32 +7706,28 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7742,13 +7742,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580969</v>
+        <v>581093</v>
       </c>
       <c r="R62" t="n">
-        <v>6384921</v>
+        <v>6384901</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7793,12 +7793,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122534099</v>
+        <v>122534080</v>
       </c>
       <c r="B58" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580969</v>
+        <v>580937</v>
       </c>
       <c r="R58" t="n">
-        <v>6384921</v>
+        <v>6384897</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7362,10 +7362,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122537789</v>
+        <v>122537449</v>
       </c>
       <c r="B59" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7374,31 +7374,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7406,10 +7410,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581038</v>
+        <v>581078</v>
       </c>
       <c r="R59" t="n">
-        <v>6384962</v>
+        <v>6384903</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7450,7 +7454,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7469,10 +7472,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537449</v>
+        <v>122537418</v>
       </c>
       <c r="B60" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7481,35 +7484,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7517,10 +7520,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581078</v>
+        <v>581093</v>
       </c>
       <c r="R60" t="n">
-        <v>6384903</v>
+        <v>6384901</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7561,6 +7564,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7579,10 +7583,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122534080</v>
+        <v>122537789</v>
       </c>
       <c r="B61" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7591,37 +7595,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7631,13 +7627,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580937</v>
+        <v>581038</v>
       </c>
       <c r="R61" t="n">
-        <v>6384897</v>
+        <v>6384962</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7682,22 +7678,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122537418</v>
+        <v>122534099</v>
       </c>
       <c r="B62" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7706,28 +7702,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7742,13 +7742,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581093</v>
+        <v>580969</v>
       </c>
       <c r="R62" t="n">
-        <v>6384901</v>
+        <v>6384921</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7793,12 +7793,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -7247,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122534080</v>
+        <v>122537418</v>
       </c>
       <c r="B58" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7259,32 +7259,28 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -7299,13 +7295,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580937</v>
+        <v>581093</v>
       </c>
       <c r="R58" t="n">
-        <v>6384897</v>
+        <v>6384901</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7350,22 +7346,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122537449</v>
+        <v>122534099</v>
       </c>
       <c r="B59" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7374,35 +7370,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7410,13 +7410,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581078</v>
+        <v>580969</v>
       </c>
       <c r="R59" t="n">
-        <v>6384903</v>
+        <v>6384921</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7454,28 +7454,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537418</v>
+        <v>122537449</v>
       </c>
       <c r="B60" t="n">
-        <v>105463</v>
+        <v>57494</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7484,35 +7485,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7520,10 +7521,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581093</v>
+        <v>581078</v>
       </c>
       <c r="R60" t="n">
-        <v>6384901</v>
+        <v>6384903</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7564,7 +7565,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7583,10 +7583,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122537789</v>
+        <v>122534080</v>
       </c>
       <c r="B61" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7595,29 +7595,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7627,13 +7635,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581038</v>
+        <v>580937</v>
       </c>
       <c r="R61" t="n">
-        <v>6384962</v>
+        <v>6384897</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7678,22 +7686,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122534099</v>
+        <v>122537789</v>
       </c>
       <c r="B62" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7702,37 +7710,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7742,13 +7742,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580969</v>
+        <v>581038</v>
       </c>
       <c r="R62" t="n">
-        <v>6384921</v>
+        <v>6384962</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7793,12 +7793,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 56737-2023 artfynd.xlsx
+++ b/artfynd/A 56737-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100669477</v>
+        <v>113291966</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fallebo, Hjorted, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580956.8226531028</v>
+        <v>581066</v>
       </c>
       <c r="R2" t="n">
-        <v>6384868.877326148</v>
+        <v>6384977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,62 +789,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100669597</v>
+        <v>113291991</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1639</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fallebo, Hjorted, Sm</t>
+          <t>A 54373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580960.775097759</v>
+        <v>581114</v>
       </c>
       <c r="R3" t="n">
-        <v>6384886.108956411</v>
+        <v>6384982</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,22 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På klen ek. A 56737</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,62 +895,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100669567</v>
+        <v>113292823</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1639</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fallebo, Hjorted, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580951.8947617216</v>
+        <v>581121</v>
       </c>
       <c r="R4" t="n">
-        <v>6384873.603154723</v>
+        <v>6384955</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,62 +996,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100669579</v>
+        <v>113292075</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fallebo, Hjorted, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580945.5830119024</v>
+        <v>581101</v>
       </c>
       <c r="R5" t="n">
-        <v>6384893.845974837</v>
+        <v>6384982</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,22 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På ekstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,62 +1103,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100669436</v>
+        <v>122537583</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fallebo, Hjorted, Sm</t>
+          <t>Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580969.0738406403</v>
+        <v>580933</v>
       </c>
       <c r="R6" t="n">
-        <v>6384873.946145277</v>
+        <v>6384991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,22 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,69 +1205,63 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100669332</v>
+        <v>122537503</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fallebo, Hjorted, Sm</t>
+          <t>Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580952.3052566443</v>
+        <v>580940</v>
       </c>
       <c r="R7" t="n">
-        <v>6384906.844636098</v>
+        <v>6384946</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,22 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,72 +1314,65 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100688290</v>
+        <v>113299787</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fallebo, Hjorted, Sm</t>
+          <t>Fallebo, Fallebo, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580958.7259634142</v>
+        <v>581095</v>
       </c>
       <c r="R8" t="n">
-        <v>6384908.044859972</v>
+        <v>6384899</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,22 +1396,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,34 +1420,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113292820</v>
+        <v>113292536</v>
       </c>
       <c r="B9" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581112</v>
+        <v>581145</v>
       </c>
       <c r="R9" t="n">
-        <v>6384959</v>
+        <v>6384896</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,51 +1547,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113292527</v>
+        <v>113292820</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581145</v>
+        <v>581112</v>
       </c>
       <c r="R10" t="n">
-        <v>6384896</v>
+        <v>6384959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,61 +1656,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113292536</v>
+        <v>122537449</v>
       </c>
       <c r="B11" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581145</v>
+        <v>581078</v>
       </c>
       <c r="R11" t="n">
-        <v>6384896</v>
+        <v>6384903</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1860,12 +1729,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,7 +1743,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1886,69 +1754,61 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113291899</v>
+        <v>113292482</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581041</v>
+        <v>580976</v>
       </c>
       <c r="R12" t="n">
-        <v>6385029</v>
+        <v>6384928</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,11 +1841,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>A 56737</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,15 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113292634</v>
+        <v>100669332</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +1898,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2061,14 +1911,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580958</v>
+        <v>580952</v>
       </c>
       <c r="R13" t="n">
-        <v>6384900</v>
+        <v>6384907</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2095,12 +1945,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2128,15 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113292345</v>
+        <v>100669436</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2018,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2176,14 +2031,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581053</v>
+        <v>580969</v>
       </c>
       <c r="R14" t="n">
-        <v>6384984</v>
+        <v>6384874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,17 +2065,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>A 56737</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,15 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113291970</v>
+        <v>100669477</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2136,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2292,14 +2151,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581060</v>
+        <v>580957</v>
       </c>
       <c r="R15" t="n">
-        <v>6384981</v>
+        <v>6384869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,17 +2185,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>A 56737</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,15 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113292603</v>
+        <v>100669567</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2397,7 +2256,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2408,14 +2271,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580962</v>
+        <v>580952</v>
       </c>
       <c r="R16" t="n">
-        <v>6384872</v>
+        <v>6384874</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2442,12 +2305,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2475,15 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113292517</v>
+        <v>100669579</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2378,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2523,14 +2391,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581151</v>
+        <v>580946</v>
       </c>
       <c r="R17" t="n">
-        <v>6384896</v>
+        <v>6384894</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2557,12 +2425,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,15 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113292406</v>
+        <v>100669597</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,7 +2498,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2638,14 +2511,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580995</v>
+        <v>580961</v>
       </c>
       <c r="R18" t="n">
-        <v>6384962</v>
+        <v>6384886</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2672,12 +2545,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,15 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113291930</v>
+        <v>100688290</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2740,7 +2618,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2753,14 +2631,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581034</v>
+        <v>580959</v>
       </c>
       <c r="R19" t="n">
-        <v>6384977</v>
+        <v>6384908</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2787,17 +2665,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>A 56737</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,15 +2698,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113291906</v>
+        <v>109006896</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2858,11 +2726,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2873,14 +2737,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581046</v>
+        <v>581026</v>
       </c>
       <c r="R20" t="n">
-        <v>6384987</v>
+        <v>6385044</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2907,17 +2771,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>A 56737</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2945,53 +2804,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113291991</v>
+        <v>109006918</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1639</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 54373, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581114</v>
+        <v>581028</v>
       </c>
       <c r="R21" t="n">
-        <v>6384982</v>
+        <v>6385050</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3018,17 +2881,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På klen ek. A 56737</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,15 +2914,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113292510</v>
+        <v>109006929</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +2944,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3104,14 +2957,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>Fallebo, Hjorted, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581137</v>
+        <v>581008</v>
       </c>
       <c r="R22" t="n">
-        <v>6384888</v>
+        <v>6385049</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3138,12 +2991,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,15 +3024,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113292573</v>
+        <v>113291899</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,7 +3052,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3215,14 +3067,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581003</v>
+        <v>581041</v>
       </c>
       <c r="R23" t="n">
-        <v>6384869</v>
+        <v>6385029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3255,6 +3107,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,15 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113292544</v>
+        <v>113291906</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3317,7 +3169,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3330,14 +3182,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581141</v>
+        <v>581046</v>
       </c>
       <c r="R24" t="n">
-        <v>6384902</v>
+        <v>6384987</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,6 +3222,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,15 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113292577</v>
+        <v>113291920</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3432,7 +3284,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3445,14 +3297,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580982</v>
+        <v>581039</v>
       </c>
       <c r="R25" t="n">
-        <v>6384886</v>
+        <v>6384990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3485,6 +3337,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,15 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113292631</v>
+        <v>113291925</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3547,7 +3399,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3564,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580973</v>
+        <v>581027</v>
       </c>
       <c r="R26" t="n">
-        <v>6384916</v>
+        <v>6384989</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3627,42 +3479,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113292625</v>
+        <v>113291930</v>
       </c>
       <c r="B27" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3675,14 +3522,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580958</v>
+        <v>581034</v>
       </c>
       <c r="R27" t="n">
-        <v>6384886</v>
+        <v>6384977</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,6 +3562,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3742,15 +3594,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113292499</v>
+        <v>113291938</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3775,7 +3622,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3786,14 +3637,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581098</v>
+        <v>581040</v>
       </c>
       <c r="R28" t="n">
-        <v>6384882</v>
+        <v>6385000</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3826,6 +3677,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3853,15 +3709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113292386</v>
+        <v>113291944</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3888,7 +3739,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3901,14 +3752,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580963</v>
+        <v>581051</v>
       </c>
       <c r="R29" t="n">
-        <v>6384950</v>
+        <v>6384990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3941,6 +3792,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3968,15 +3824,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113292428</v>
+        <v>113291970</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4001,11 +3852,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4016,14 +3863,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581076</v>
+        <v>581060</v>
       </c>
       <c r="R30" t="n">
-        <v>6384923</v>
+        <v>6384981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4056,6 +3903,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,53 +3935,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113292823</v>
+        <v>113291978</v>
       </c>
       <c r="B31" t="n">
-        <v>78707</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1639</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581121</v>
+        <v>581061</v>
       </c>
       <c r="R31" t="n">
-        <v>6384955</v>
+        <v>6384994</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4162,6 +4018,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4189,15 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113292593</v>
+        <v>113292338</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4224,7 +4080,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4237,14 +4093,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580969</v>
+        <v>581055</v>
       </c>
       <c r="R32" t="n">
-        <v>6384870</v>
+        <v>6384999</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4277,6 +4133,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4304,15 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113292435</v>
+        <v>113292345</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4339,7 +4195,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4352,14 +4208,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 56737, Gölpefall, Sm</t>
+          <t>A 56373, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581003</v>
+        <v>581053</v>
       </c>
       <c r="R33" t="n">
-        <v>6384915</v>
+        <v>6384984</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4392,6 +4248,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>A 56737</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4419,15 +4280,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113292338</v>
+        <v>113292373</v>
       </c>
       <c r="B34" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4454,7 +4310,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4467,14 +4323,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581055</v>
+        <v>581014</v>
       </c>
       <c r="R34" t="n">
-        <v>6384999</v>
+        <v>6384956</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4507,11 +4363,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>A 56737</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4539,15 +4390,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113292373</v>
+        <v>113292378</v>
       </c>
       <c r="B35" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4574,7 +4420,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4591,10 +4437,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581014</v>
+        <v>580992</v>
       </c>
       <c r="R35" t="n">
-        <v>6384956</v>
+        <v>6384972</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,15 +4500,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113292442</v>
+        <v>113292386</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4530,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4706,10 +4547,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581062</v>
+        <v>580963</v>
       </c>
       <c r="R36" t="n">
-        <v>6384865</v>
+        <v>6384950</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4769,15 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113292610</v>
+        <v>113292406</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4802,7 +4638,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4817,10 +4657,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580937</v>
+        <v>580995</v>
       </c>
       <c r="R37" t="n">
-        <v>6384883</v>
+        <v>6384962</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4880,15 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113291925</v>
+        <v>113292428</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4915,7 +4750,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4932,10 +4767,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581027</v>
+        <v>581076</v>
       </c>
       <c r="R38" t="n">
-        <v>6384989</v>
+        <v>6384923</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4995,15 +4830,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113291978</v>
+        <v>113292435</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5030,7 +4860,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5043,14 +4873,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581061</v>
+        <v>581003</v>
       </c>
       <c r="R39" t="n">
-        <v>6384994</v>
+        <v>6384915</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5083,11 +4913,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>A 56737</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5115,15 +4940,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113292641</v>
+        <v>113292442</v>
       </c>
       <c r="B40" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5150,7 +4970,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5167,10 +4987,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580973</v>
+        <v>581062</v>
       </c>
       <c r="R40" t="n">
-        <v>6384935</v>
+        <v>6384865</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5230,48 +5050,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113292482</v>
+        <v>113292451</v>
       </c>
       <c r="B41" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5279,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580976</v>
+        <v>580975</v>
       </c>
       <c r="R41" t="n">
-        <v>6384928</v>
+        <v>6384923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5342,15 +5160,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113292557</v>
+        <v>113292464</v>
       </c>
       <c r="B42" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5190,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5394,10 +5207,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580970</v>
+        <v>580972</v>
       </c>
       <c r="R42" t="n">
-        <v>6384887</v>
+        <v>6384972</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5457,15 +5270,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113291944</v>
+        <v>113292499</v>
       </c>
       <c r="B43" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,11 +5298,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -5505,14 +5309,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581051</v>
+        <v>581098</v>
       </c>
       <c r="R43" t="n">
-        <v>6384990</v>
+        <v>6384882</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5545,11 +5349,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>A 56737</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5577,15 +5376,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113291920</v>
+        <v>113292510</v>
       </c>
       <c r="B44" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5625,14 +5419,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581039</v>
+        <v>581137</v>
       </c>
       <c r="R44" t="n">
-        <v>6384990</v>
+        <v>6384888</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5665,11 +5459,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>A 56737</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5697,15 +5486,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113292451</v>
+        <v>113292517</v>
       </c>
       <c r="B45" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5732,7 +5516,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5749,10 +5533,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580975</v>
+        <v>581151</v>
       </c>
       <c r="R45" t="n">
-        <v>6384923</v>
+        <v>6384896</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5812,15 +5596,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113292581</v>
+        <v>113292527</v>
       </c>
       <c r="B46" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5847,7 +5626,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5864,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580973</v>
+        <v>581145</v>
       </c>
       <c r="R46" t="n">
-        <v>6384887</v>
+        <v>6384896</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5927,15 +5706,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113291938</v>
+        <v>113292544</v>
       </c>
       <c r="B47" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5962,7 +5736,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5975,14 +5749,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581040</v>
+        <v>581141</v>
       </c>
       <c r="R47" t="n">
-        <v>6385000</v>
+        <v>6384902</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6015,11 +5789,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>A 56737</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6047,15 +5816,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113292464</v>
+        <v>113292557</v>
       </c>
       <c r="B48" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6082,7 +5846,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6099,10 +5863,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580972</v>
+        <v>580970</v>
       </c>
       <c r="R48" t="n">
-        <v>6384972</v>
+        <v>6384887</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6162,61 +5926,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>113291966</v>
+        <v>113292573</v>
       </c>
       <c r="B49" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>A 56373, Gölpefall, Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581066</v>
+        <v>581003</v>
       </c>
       <c r="R49" t="n">
-        <v>6384977</v>
+        <v>6384869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6249,11 +6005,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>A 56737</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6281,15 +6032,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>113301919</v>
+        <v>113292577</v>
       </c>
       <c r="B50" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6316,7 +6062,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6325,19 +6071,21 @@
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fallebo (Fallebo), Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580993</v>
+        <v>580982</v>
       </c>
       <c r="R50" t="n">
-        <v>6384951</v>
+        <v>6384886</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6361,22 +6109,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6385,33 +6123,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113302008</v>
+        <v>113292581</v>
       </c>
       <c r="B51" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6438,7 +6172,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6447,19 +6181,21 @@
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fallebo (Fallebo), Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581009</v>
+        <v>580973</v>
       </c>
       <c r="R51" t="n">
-        <v>6384934</v>
+        <v>6384887</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6483,22 +6219,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6507,59 +6233,63 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113292075</v>
+        <v>113292593</v>
       </c>
       <c r="B52" t="n">
-        <v>94147</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2671</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6569,10 +6299,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581101</v>
+        <v>580969</v>
       </c>
       <c r="R52" t="n">
-        <v>6384982</v>
+        <v>6384870</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6605,11 +6335,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2023-11-17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På ekstam</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6637,15 +6362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113301491</v>
+        <v>113292603</v>
       </c>
       <c r="B53" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6670,30 +6390,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fallebo (Fallebo), Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581031</v>
+        <v>580962</v>
       </c>
       <c r="R53" t="n">
-        <v>6384977</v>
+        <v>6384872</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6717,22 +6435,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6741,33 +6449,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113301537</v>
+        <v>113292610</v>
       </c>
       <c r="B54" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6792,30 +6496,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fallebo (Fallebo), Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581030</v>
+        <v>580937</v>
       </c>
       <c r="R54" t="n">
-        <v>6384986</v>
+        <v>6384883</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6839,22 +6541,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6863,33 +6555,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113301861</v>
+        <v>113292631</v>
       </c>
       <c r="B55" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6916,7 +6604,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6925,19 +6613,21 @@
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fallebo (Fallebo), Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580990</v>
+        <v>580973</v>
       </c>
       <c r="R55" t="n">
-        <v>6384978</v>
+        <v>6384916</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6961,22 +6651,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:32</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6985,81 +6665,79 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113299787</v>
+        <v>113292634</v>
       </c>
       <c r="B56" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fallebo (Fallebo), Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581095</v>
+        <v>580958</v>
       </c>
       <c r="R56" t="n">
-        <v>6384899</v>
+        <v>6384900</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7083,22 +6761,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7107,33 +6775,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113302158</v>
+        <v>113292641</v>
       </c>
       <c r="B57" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7160,7 +6824,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7169,19 +6833,21 @@
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fallebo (Fallebo), Sm</t>
+          <t>A 56737, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581024</v>
+        <v>580973</v>
       </c>
       <c r="R57" t="n">
-        <v>6384848</v>
+        <v>6384935</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7205,22 +6871,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:51</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7229,79 +6885,77 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122537418</v>
+        <v>113301491</v>
       </c>
       <c r="B58" t="n">
-        <v>105463</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gölpefall, Sm</t>
+          <t>Fallebo, Fallebo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581093</v>
+        <v>581031</v>
       </c>
       <c r="R58" t="n">
-        <v>6384901</v>
+        <v>6384977</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7325,12 +6979,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7339,34 +7003,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122534099</v>
+        <v>113301537</v>
       </c>
       <c r="B59" t="n">
-        <v>98357</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7393,7 +7051,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7402,21 +7060,19 @@
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gölpefall, Sm</t>
+          <t>Fallebo, Fallebo, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580969</v>
+        <v>581030</v>
       </c>
       <c r="R59" t="n">
-        <v>6384921</v>
+        <v>6384986</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7440,12 +7096,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7454,80 +7120,76 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122537449</v>
+        <v>113301861</v>
       </c>
       <c r="B60" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gölpefall, Sm</t>
+          <t>Fallebo, Fallebo, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581078</v>
+        <v>580990</v>
       </c>
       <c r="R60" t="n">
-        <v>6384903</v>
+        <v>6384978</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7551,12 +7213,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7571,27 +7243,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122534080</v>
+        <v>113301919</v>
       </c>
       <c r="B61" t="n">
-        <v>98357</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7618,7 +7285,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7627,21 +7294,19 @@
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gölpefall, Sm</t>
+          <t>Fallebo, Fallebo, Sm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580937</v>
+        <v>580993</v>
       </c>
       <c r="R61" t="n">
-        <v>6384897</v>
+        <v>6384951</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7665,12 +7330,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7679,76 +7354,76 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122537789</v>
+        <v>113301962</v>
       </c>
       <c r="B62" t="n">
-        <v>105463</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gölpefall, Sm</t>
+          <t>Fallebo, Fallebo, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581038</v>
+        <v>580985</v>
       </c>
       <c r="R62" t="n">
-        <v>6384962</v>
+        <v>6384963</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7772,12 +7447,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7786,22 +7471,793 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>113302008</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fallebo, Fallebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>581009</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6384934</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>113302158</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fallebo, Fallebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>581024</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6384848</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122534080</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>580937</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6384897</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>122534099</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>580969</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6384921</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>113292625</v>
+      </c>
+      <c r="B67" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>A 56737, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>580958</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6384886</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-11-17</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122537418</v>
+      </c>
+      <c r="B68" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>581093</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6384901</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122537789</v>
+      </c>
+      <c r="B69" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>581038</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6384962</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
